--- a/data/trans_dic/IP07_C14_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 14,84</t>
+          <t>7,78; 20,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 21,5</t>
+          <t>3,92; 15,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,95</t>
+          <t>7,27; 15,49</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 22,27</t>
+          <t>7,7; 19,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 20,16</t>
+          <t>13,25; 25,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,95</t>
+          <t>11,17; 19,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,09</t>
+          <t>8,94; 17,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,41</t>
+          <t>11,18; 19,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,33</t>
+          <t>10,57; 16,58</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17604</t>
         </is>
       </c>
     </row>
@@ -828,17 +828,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2581; 9845</t>
+          <t>7122; 18362</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7765; 19826</t>
+          <t>2742; 10532</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11833; 25298</t>
+          <t>11733; 24995</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42019</t>
+          <t>41280</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10200; 30192</t>
+          <t>12130; 30224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13062; 31989</t>
+          <t>15715; 29714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28180; 55775</t>
+          <t>30858; 52898</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16535; 36535</t>
+          <t>22255; 42528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24269; 46183</t>
+          <t>21073; 36454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45397; 73927</t>
+          <t>46261; 72535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C14_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C14_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,239 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,78; 20,07</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3,92; 15,06</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 15,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,7; 19,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13,25; 25,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,17; 19,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8,94; 17,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 19,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,57; 16,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:A7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -777,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1307849481773912</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.08063621033571358</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1090603897083441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11965</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5638</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17604</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.07784400442537807</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.03921439978501385</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.07268772310424503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7122; 18362</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2742; 10532</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11733; 24995</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2007054597440991</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1506164279333008</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1548505583590642</v>
       </c>
     </row>
     <row r="7">
@@ -850,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1245561161651053</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1825866142675505</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.14947441470093</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19628</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21652</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41280</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07697525516265187</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1325206443737493</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1117360986569001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12130; 30224</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15715; 29714</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30858; 52898</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1918011941562116</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2505683120182099</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.191543899777478</v>
       </c>
     </row>
     <row r="10">
@@ -923,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.126844091474199</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1447701304171976</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.134566677027244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>31593</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>27291</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58883</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.08935487176589624</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1117886073694327</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1057216195365285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>22255; 42528</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>21073; 36454</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46261; 72535</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1707497838914276</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.193378280641898</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1657644140181148</v>
       </c>
     </row>
     <row r="13">
@@ -1004,4 +725,303 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores en cuyo colegio/instituto se han producido situaciones de cyberbulling (tasa de respuesta: 94,11%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>11965</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5638</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>17604</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7122</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2742</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>11733</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>18362</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10532</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>24995</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>19628</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21652</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>41280</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12130</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15715</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>30858</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30224</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29714</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>52898</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>31593</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>27291</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>58883</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>22255</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>21073</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>42528</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>36454</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>72535</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A12:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>